--- a/evaluaciones/trabajos/feedback-ia1.xlsx
+++ b/evaluaciones/trabajos/feedback-ia1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sebastian\Desktop\PRODUCCION\00. ACCIÓN PROXIMA\03. CUANTI\Curso Cuanti 2\Curso UAH\2025\metodoscuanti2\evaluaciones\trabajos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948D11E8-0F80-4FF0-ABC3-D8E73984FA57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E806CDF-DB38-4083-91E7-316BA526A8EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="7485" windowWidth="22313" windowHeight="7568" xr2:uid="{131001DE-E294-4C02-98C9-1C5D6B184FBE}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="15196" xr2:uid="{131001DE-E294-4C02-98C9-1C5D6B184FBE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>Grupo</t>
   </si>
@@ -129,15 +129,9 @@
     <t>4- Seguridad</t>
   </si>
   <si>
-    <t xml:space="preserve"> 1) preguntas filtro; 2) explicitación de definiciones; 3) exhaustividad de géneros</t>
-  </si>
-  <si>
     <t xml:space="preserve">CD_07. ¿Considera relevante que el docente tenga disponibilidad horaria fuera de clases para responder a las dudas de los estudiantes? /  muy parecida a/ CD_08. ¿Qué tan importante es para usted que el docente sea accesible para comunicarse con los estudiantes fuera del aula (por correo, reuniones virtuales u otros medios)? </t>
   </si>
   <si>
-    <t>1) Inicialmente sólo entregaron 5 preguntas</t>
-  </si>
-  <si>
     <t xml:space="preserve">PM_08. ¿En qué lugar suele crear música? (Debe indicar que se contesta sólo si la persona ha creado música: </t>
   </si>
   <si>
@@ -153,13 +147,7 @@
     <t>AS_04. ¿Conoce alguna de las siguientes formas de infecciones de transmisión sexual (ITS)?  (Redacción)</t>
   </si>
   <si>
-    <t>1) atraso en la entrega del informe de un día</t>
-  </si>
-  <si>
     <t xml:space="preserve">PM_10. ¿En qué lugar suele tocar música?: Especificar si es que toca música, contestar), esta pregunta debería ser múltiple; 2) se sugiere poner antes esta pregunta. </t>
-  </si>
-  <si>
-    <t>1)  Sólo deben ser 10; 2) Evitar el response set; que las respuestas siempre tenga misma orientación y cantidad de alternativas (GRRSS: variar formato de pregunta); 3) lenguaje inclusivo: él o la docente</t>
   </si>
   <si>
     <r>
@@ -188,10 +176,49 @@
     </r>
   </si>
   <si>
-    <t>1) pertenencia a pueblos originarios; 2) Chileno (extranjero)</t>
-  </si>
-  <si>
     <t>1) Exhaustividad de alternativas (e.g. Kpop, r&amp;b, trap)</t>
+  </si>
+  <si>
+    <t>1)  Sólo deben ser 10; hay preguntas similiares que pueden fusionarse CD12 y CD13, por ejemplo;  2) Evitar el response set; que las respuestas siempre tenga misma orientación y cantidad de alternativas (GRRSS: variar formato de pregunta); 3) lenguaje inclusivo: él o la docente; 4</t>
+  </si>
+  <si>
+    <t>AS_12. ¿Considera que las prácticas de autocuidado sexual que utiliza son efectivas para prevenir infecciones de transmisión sexual y embarazos no deseados? (Es algo evidente, puede reformularla, dandole un costo)</t>
+  </si>
+  <si>
+    <t>24:00 (porqué 45 J. Kiessling)</t>
+  </si>
+  <si>
+    <t>Además apunta a si o no, más que al grado como está en las alternati as</t>
+  </si>
+  <si>
+    <t>1) atraso en la entrega del informe de un día; 2) Agregar una pregunta sobre tipos de uso; 3) Pareciera exisistir un sesgo negativo ante las RRSS (¿Qué pasa si alguien las usa para trabajar?)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1) preguntas filtro; 2) explicitación de definiciones; 3) exhaustividad de géneros; 4) no es necesario ser tan explícito sobre los objetivos de su investigación: El objetivo de esta investigación es analizar y describir las prácticas musicales de los
+estudiantes de antropología de la Universidad Alberto Hurtado, y su relación con los factores
+de identidad de género y clase socioeconómica.</t>
+  </si>
+  <si>
+    <t>Integrar alternativa "Sin Estudios"</t>
+  </si>
+  <si>
+    <t>RS_01. ¿Con qué frecuencia usa las redes sociales en actividades que no son laborales ni académicas?  (Delimitar el tiempo, al dia, a la semana?)</t>
+  </si>
+  <si>
+    <t>RS_03. ¿Cuál es la red social en la que pasa más tiempo? : sumar cuál es la segunda RRSS</t>
+  </si>
+  <si>
+    <t>Sumar la opción: no uso RRSS</t>
+  </si>
+  <si>
+    <t>a) se podría incluir la alternativa en casa; b) En eventos de amigues vs. En reuniones de amigos y familiares ??</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) pertenencia a pueblos originarios; 2) Nacionalidad (extranjero); 3) medio de transporte privilegiado; 4) ¿Es originario de la región metropolitana, esto es vivió la mayor parte de su infancia y adolecencia fuera de esta región?; 5) aclarar niveles educativos ( Técnico nivel superior (como técnico en enfermería, técnico en administración, etc.);  Profesional (carreras universitarias como ingeniería, derecho, etc.)
+</t>
+  </si>
+  <si>
+    <t>1) Inicialmente sólo entregaron 5 preguntas; b) diferencia día y noche</t>
   </si>
 </sst>
 </file>
@@ -258,7 +285,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -282,6 +309,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -598,15 +628,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8C81278-1577-4240-9DEA-C045D773234E}">
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:X9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="16.86328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="23" width="9.6640625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="15.06640625" style="8" customWidth="1"/>
+    <col min="4" max="23" width="9.6640625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:24">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -675,13 +706,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="63">
+    <row r="2" spans="1:24" ht="42">
       <c r="A2" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
@@ -704,7 +735,7 @@
       <c r="V2" s="5"/>
       <c r="W2" s="5"/>
     </row>
-    <row r="3" spans="1:23" ht="52.5">
+    <row r="3" spans="1:24" ht="210">
       <c r="A3" s="2" t="s">
         <v>23</v>
       </c>
@@ -712,7 +743,7 @@
         <v>0.43333333333333335</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
@@ -727,7 +758,9 @@
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
+      <c r="Q3" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="R3" s="5"/>
       <c r="S3" s="5"/>
       <c r="T3" s="5"/>
@@ -735,7 +768,7 @@
       <c r="V3" s="5"/>
       <c r="W3" s="5"/>
     </row>
-    <row r="4" spans="1:23" ht="357">
+    <row r="4" spans="1:24" ht="357">
       <c r="A4" s="2" t="s">
         <v>24</v>
       </c>
@@ -743,14 +776,19 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
+        <v>46</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>49</v>
+      </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
+      <c r="H4" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
@@ -758,7 +796,9 @@
       <c r="N4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="O4" s="1"/>
+      <c r="O4" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
@@ -770,7 +810,7 @@
       </c>
       <c r="W4" s="5"/>
     </row>
-    <row r="5" spans="1:23" ht="324">
+    <row r="5" spans="1:24" ht="324">
       <c r="A5" s="2" t="s">
         <v>25</v>
       </c>
@@ -778,11 +818,11 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -803,23 +843,27 @@
       </c>
       <c r="Q5" s="5"/>
       <c r="R5" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="S5" s="5"/>
       <c r="T5" s="5"/>
       <c r="U5" s="5"/>
       <c r="V5" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="W5" s="5"/>
+        <v>39</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="6" spans="1:23" ht="313.89999999999998">
+    <row r="6" spans="1:24" ht="313.89999999999998">
       <c r="A6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="2"/>
+      <c r="B6" s="3">
+        <v>0.5</v>
+      </c>
       <c r="C6" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
@@ -835,24 +879,26 @@
       <c r="O6" s="5"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R6" s="7"/>
       <c r="S6" s="5"/>
       <c r="T6" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="U6" s="5"/>
       <c r="V6" s="7"/>
       <c r="W6" s="5"/>
     </row>
-    <row r="7" spans="1:23" ht="73.900000000000006" customHeight="1">
+    <row r="7" spans="1:24" ht="42.75">
       <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="C7" s="5" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -875,13 +921,15 @@
       <c r="V7" s="5"/>
       <c r="W7" s="5"/>
     </row>
-    <row r="8" spans="1:23" ht="94.5">
+    <row r="8" spans="1:24" ht="91.9">
       <c r="A8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8" s="3">
+        <v>0.91666666666666663</v>
+      </c>
       <c r="C8" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
@@ -890,7 +938,7 @@
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
       <c r="J8" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
@@ -905,8 +953,11 @@
       <c r="U8" s="5"/>
       <c r="V8" s="5"/>
       <c r="W8" s="5"/>
+      <c r="X8" s="4" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:24">
       <c r="B9" s="2"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -927,5 +978,6 @@
   <autoFilter ref="A1:W1" xr:uid="{F8C81278-1577-4240-9DEA-C045D773234E}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/evaluaciones/trabajos/feedback-ia1.xlsx
+++ b/evaluaciones/trabajos/feedback-ia1.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sebastian\Desktop\PRODUCCION\00. ACCIÓN PROXIMA\03. CUANTI\Curso Cuanti 2\Curso UAH\2025\metodoscuanti2\evaluaciones\trabajos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E806CDF-DB38-4083-91E7-316BA526A8EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA3EA3F-23EA-4E37-A6D9-04123D8ACCAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="15196" xr2:uid="{131001DE-E294-4C02-98C9-1C5D6B184FBE}"/>
+    <workbookView xWindow="285" yWindow="667" windowWidth="20220" windowHeight="5341" activeTab="1" xr2:uid="{131001DE-E294-4C02-98C9-1C5D6B184FBE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$W$1</definedName>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="68">
   <si>
     <t>Grupo</t>
   </si>
@@ -220,11 +221,53 @@
   <si>
     <t>1) Inicialmente sólo entregaron 5 preguntas; b) diferencia día y noche</t>
   </si>
+  <si>
+    <t>0-Canala, Castro, Durán</t>
+  </si>
+  <si>
+    <t>1-Huineo, Verdugo, Salazar, Leiva</t>
+  </si>
+  <si>
+    <t>3-Bickell, Campos, Kiessling, Mancilla, Nuñez</t>
+  </si>
+  <si>
+    <t>4-Catejo, Farías, Fis, Lagos, Sanchez, Valenzuela, Valle</t>
+  </si>
+  <si>
+    <t>5-Araya, La Rivera, Muñoz, Navarro, Parker, Rudman</t>
+  </si>
+  <si>
+    <t>sección tiempos</t>
+  </si>
+  <si>
+    <t>sessión retroalimentación</t>
+  </si>
+  <si>
+    <t>sección cuestionario</t>
+  </si>
+  <si>
+    <t>sección indice</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t>nota</t>
+  </si>
+  <si>
+    <t>atraso</t>
+  </si>
+  <si>
+    <t>2-Jorquera, Salazar, Diaz, González, González, Bustamante</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <sz val="11"/>
@@ -265,12 +308,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -285,7 +334,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -314,6 +363,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -980,4 +1032,202 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7501C75E-EE71-47C2-9197-CC9A2298112A}">
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="43" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.1328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.86328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2">
+        <v>100</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
+      </c>
+      <c r="D2">
+        <v>90</v>
+      </c>
+      <c r="E2">
+        <f>AVERAGE(B2:D2)</f>
+        <v>96.666666666666671</v>
+      </c>
+      <c r="F2">
+        <f t="shared" ref="F2:F7" si="0">(B2*0.1)+(C2*0.2)+((D2+E2)/2*0.7)</f>
+        <v>95.333333333333343</v>
+      </c>
+      <c r="G2" s="10">
+        <f t="shared" ref="G2:G7" si="1">F2*7/100</f>
+        <v>6.6733333333333338</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3">
+        <v>100</v>
+      </c>
+      <c r="C3">
+        <v>100</v>
+      </c>
+      <c r="D3">
+        <v>70</v>
+      </c>
+      <c r="E3">
+        <v>75</v>
+      </c>
+      <c r="F3">
+        <f t="shared" si="0"/>
+        <v>80.75</v>
+      </c>
+      <c r="G3" s="10">
+        <f t="shared" si="1"/>
+        <v>5.6524999999999999</v>
+      </c>
+      <c r="H3" s="10">
+        <f>G3-0.25</f>
+        <v>5.4024999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="11" customFormat="1">
+      <c r="A4" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="11">
+        <v>90</v>
+      </c>
+      <c r="C4" s="11">
+        <v>100</v>
+      </c>
+      <c r="D4" s="11">
+        <v>80</v>
+      </c>
+      <c r="E4" s="11">
+        <v>80</v>
+      </c>
+      <c r="F4" s="11">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+      <c r="G4" s="12">
+        <f t="shared" si="1"/>
+        <v>5.95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5">
+        <v>80</v>
+      </c>
+      <c r="C5">
+        <v>80</v>
+      </c>
+      <c r="D5">
+        <v>70</v>
+      </c>
+      <c r="E5">
+        <v>75</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>74.75</v>
+      </c>
+      <c r="G5" s="10">
+        <f t="shared" si="1"/>
+        <v>5.2324999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6">
+        <v>90</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6">
+        <v>85</v>
+      </c>
+      <c r="E6">
+        <v>60</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>79.75</v>
+      </c>
+      <c r="G6" s="10">
+        <f t="shared" si="1"/>
+        <v>5.5824999999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7">
+        <v>80</v>
+      </c>
+      <c r="C7">
+        <v>80</v>
+      </c>
+      <c r="D7">
+        <v>90</v>
+      </c>
+      <c r="E7">
+        <v>80</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>83.5</v>
+      </c>
+      <c r="G7" s="10">
+        <f t="shared" si="1"/>
+        <v>5.8449999999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>